--- a/data/trans_dic/P62-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P62-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que percibe algun tipo de pensión</t>
+          <t>Población que percibe algun tipo de pensión (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,01; 59,01</t>
+          <t>39,23; 58,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,8; 53,54</t>
+          <t>37,97; 54,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,43; 45,96</t>
+          <t>29,96; 45,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,5; 28,93</t>
+          <t>14,26; 28,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,92; 32,45</t>
+          <t>17,41; 31,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,94; 44,09</t>
+          <t>29,55; 44,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,49; 36,81</t>
+          <t>23,67; 37,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,73; 27,16</t>
+          <t>16,78; 26,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,1; 41,22</t>
+          <t>29,21; 41,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,37; 46,4</t>
+          <t>35,33; 46,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,59; 39,54</t>
+          <t>28,12; 38,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,16; 26,03</t>
+          <t>16,95; 25,95</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,41; 61,74</t>
+          <t>48,41; 61,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,6; 46,08</t>
+          <t>34,66; 46,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,94; 51,36</t>
+          <t>39,86; 51,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41,63; 58,24</t>
+          <t>41,84; 58,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,24; 25,51</t>
+          <t>17,41; 26,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,33; 27,8</t>
+          <t>18,93; 27,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,2; 27,23</t>
+          <t>18,38; 27,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,69; 40,59</t>
+          <t>31,66; 40,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,7; 38,07</t>
+          <t>30,58; 38,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,74; 34,13</t>
+          <t>27,26; 34,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,2; 36,28</t>
+          <t>29,25; 36,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,01; 46,58</t>
+          <t>37,8; 46,78</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44,88; 61,92</t>
+          <t>44,06; 61,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,55; 53,18</t>
+          <t>38,48; 53,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,52; 55,29</t>
+          <t>40,85; 55,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46,56; 62,62</t>
+          <t>47,42; 62,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,95; 33,82</t>
+          <t>22,61; 33,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,08; 35,84</t>
+          <t>23,87; 35,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,63; 38,66</t>
+          <t>26,52; 39,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,83; 41,48</t>
+          <t>31,81; 42,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32,34; 41,88</t>
+          <t>32,12; 41,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31,55; 40,51</t>
+          <t>31,74; 40,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,49; 43,88</t>
+          <t>34,77; 44,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40,14; 49,32</t>
+          <t>40,32; 49,0</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>44,0; 60,44</t>
+          <t>43,73; 60,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,92; 50,98</t>
+          <t>38,66; 51,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,06; 44,41</t>
+          <t>31,98; 44,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42,71; 64,46</t>
+          <t>43,99; 64,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,45; 33,32</t>
+          <t>22,06; 33,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,88; 42,38</t>
+          <t>30,96; 41,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,06; 32,84</t>
+          <t>22,22; 33,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,22; 42,73</t>
+          <t>32,5; 42,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,85; 41,49</t>
+          <t>31,71; 41,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35,23; 44,41</t>
+          <t>36,08; 44,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,14; 36,88</t>
+          <t>28,36; 36,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,26; 49,34</t>
+          <t>39,34; 49,42</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,18; 62,7</t>
+          <t>42,07; 62,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,93; 47,92</t>
+          <t>30,51; 48,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42,61; 60,99</t>
+          <t>42,91; 60,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37,45; 59,6</t>
+          <t>38,16; 60,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,76; 29,41</t>
+          <t>16,12; 29,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,04; 36,79</t>
+          <t>22,13; 36,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,68; 42,87</t>
+          <t>27,15; 42,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,8; 48,46</t>
+          <t>35,37; 48,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26,87; 38,94</t>
+          <t>27,3; 39,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27,19; 38,42</t>
+          <t>28,05; 39,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,32; 48,01</t>
+          <t>37,1; 47,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,64; 49,52</t>
+          <t>38,22; 49,94</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>46,4; 64,56</t>
+          <t>46,47; 64,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40,31; 56,08</t>
+          <t>39,96; 55,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39,3; 54,79</t>
+          <t>39,73; 55,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51,67; 67,6</t>
+          <t>51,0; 67,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,35; 30,7</t>
+          <t>18,78; 31,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,08; 32,9</t>
+          <t>21,55; 33,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,94; 30,11</t>
+          <t>17,33; 30,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30,0; 40,64</t>
+          <t>29,46; 40,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30,72; 41,64</t>
+          <t>29,83; 40,89</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,97; 40,63</t>
+          <t>30,46; 40,55</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28,24; 38,91</t>
+          <t>29,43; 39,49</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>41,3; 50,28</t>
+          <t>40,76; 50,11</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>44,87; 57,21</t>
+          <t>45,29; 57,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36,81; 47,33</t>
+          <t>36,82; 46,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46,53; 58,54</t>
+          <t>46,11; 58,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47,36; 62,14</t>
+          <t>47,78; 62,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,07; 30,3</t>
+          <t>21,55; 30,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,56; 34,09</t>
+          <t>25,41; 33,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,24; 43,79</t>
+          <t>33,37; 43,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>41,51; 86,81</t>
+          <t>41,25; 88,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>32,0; 39,05</t>
+          <t>32,44; 38,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31,79; 38,33</t>
+          <t>31,24; 38,49</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40,8; 48,56</t>
+          <t>40,93; 48,64</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,26; 83,28</t>
+          <t>47,48; 81,28</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>55,72; 67,17</t>
+          <t>55,5; 67,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>42,29; 52,83</t>
+          <t>42,37; 52,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43,09; 52,73</t>
+          <t>42,91; 52,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61,03; 73,68</t>
+          <t>61,5; 73,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,56; 28,14</t>
+          <t>20,12; 27,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,87; 31,54</t>
+          <t>23,6; 31,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,93; 35,5</t>
+          <t>27,4; 35,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>36,13; 43,81</t>
+          <t>36,15; 43,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32,86; 40,12</t>
+          <t>32,82; 39,8</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32,87; 39,37</t>
+          <t>32,92; 39,02</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35,62; 42,0</t>
+          <t>35,58; 42,02</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>48,02; 54,27</t>
+          <t>47,99; 54,4</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>51,84; 57,23</t>
+          <t>51,94; 57,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41,5; 46,28</t>
+          <t>41,76; 46,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44,11; 48,56</t>
+          <t>44,08; 48,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51,19; 57,15</t>
+          <t>51,16; 57,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22,8; 26,4</t>
+          <t>22,96; 26,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,18; 30,79</t>
+          <t>27,43; 30,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,31; 32,25</t>
+          <t>28,23; 32,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>36,79; 62,01</t>
+          <t>36,89; 59,56</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>34,06; 37,23</t>
+          <t>34,13; 37,28</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34,16; 37,13</t>
+          <t>34,15; 36,95</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35,94; 38,83</t>
+          <t>35,76; 38,64</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>44,09; 59,01</t>
+          <t>44,13; 58,3</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que percibe algun tipo de pensión</t>
+          <t>Población que percibe algun tipo de pensión (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43051; 63499</t>
+          <t>42220; 62620</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63108; 89378</t>
+          <t>63394; 91038</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47708; 72063</t>
+          <t>46985; 71789</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15647; 33523</t>
+          <t>16523; 33008</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26668; 48307</t>
+          <t>25914; 47001</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54408; 82896</t>
+          <t>55571; 83801</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41199; 67427</t>
+          <t>43355; 68542</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24316; 39458</t>
+          <t>24379; 39191</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74620; 105717</t>
+          <t>74908; 105458</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>125572; 164704</t>
+          <t>125406; 164959</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>97199; 134428</t>
+          <t>95594; 131838</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44828; 67999</t>
+          <t>44275; 67792</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>107758; 137431</t>
+          <t>107765; 137682</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>113923; 151718</t>
+          <t>114128; 151731</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>130795; 168175</t>
+          <t>130532; 167579</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>111975; 156662</t>
+          <t>112546; 157882</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63665; 94230</t>
+          <t>64308; 96703</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72142; 109427</t>
+          <t>74503; 109368</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74296; 111143</t>
+          <t>75009; 110850</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>108028; 138353</t>
+          <t>107931; 138054</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181732; 225319</t>
+          <t>180999; 226374</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>193309; 246695</t>
+          <t>197035; 252860</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>214838; 266891</t>
+          <t>215154; 267229</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>231823; 284066</t>
+          <t>230554; 285318</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>64236; 88629</t>
+          <t>63072; 87370</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>67554; 95662</t>
+          <t>69223; 95496</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77222; 102837</t>
+          <t>75979; 102930</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77465; 104186</t>
+          <t>78898; 104381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>52874; 81443</t>
+          <t>54449; 80725</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61795; 91979</t>
+          <t>61260; 91024</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65438; 95011</t>
+          <t>65184; 95907</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>72281; 94192</t>
+          <t>72240; 95867</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>124198; 160822</t>
+          <t>123323; 160881</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>137719; 176806</t>
+          <t>138540; 178628</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>148919; 189453</t>
+          <t>150096; 191174</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>157953; 194040</t>
+          <t>158649; 192816</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59024; 81084</t>
+          <t>58656; 80572</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>86605; 116449</t>
+          <t>88304; 117997</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80791; 111918</t>
+          <t>80586; 111037</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61381; 92650</t>
+          <t>63227; 92849</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52845; 78425</t>
+          <t>51929; 78451</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>86670; 118936</t>
+          <t>86887; 117632</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66022; 98312</t>
+          <t>66508; 99751</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69271; 91870</t>
+          <t>69887; 91791</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>117696; 153296</t>
+          <t>117182; 154133</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>179319; 226076</t>
+          <t>183638; 228671</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>155163; 203332</t>
+          <t>156338; 198842</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>140844; 177003</t>
+          <t>141114; 177293</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36566; 54353</t>
+          <t>36466; 54297</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>38686; 61939</t>
+          <t>39438; 62835</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55517; 79464</t>
+          <t>55907; 78343</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24156; 38446</t>
+          <t>24613; 38953</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24777; 46247</t>
+          <t>25349; 45790</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35894; 59930</t>
+          <t>36051; 60004</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44881; 69516</t>
+          <t>44032; 69375</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>34949; 48668</t>
+          <t>35523; 48320</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>65537; 94996</t>
+          <t>66605; 95535</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>79439; 112245</t>
+          <t>81943; 114793</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>109142; 140400</t>
+          <t>108499; 139706</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>63730; 81676</t>
+          <t>63036; 82364</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>52771; 73431</t>
+          <t>52853; 73735</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>62352; 86742</t>
+          <t>61807; 86235</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61165; 85264</t>
+          <t>61823; 86332</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69533; 90975</t>
+          <t>68637; 91088</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>35837; 59969</t>
+          <t>36685; 61833</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47376; 73930</t>
+          <t>48436; 75438</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32675; 58077</t>
+          <t>33428; 57900</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>51200; 69354</t>
+          <t>50277; 68298</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>94936; 128685</t>
+          <t>92191; 126388</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>117488; 154171</t>
+          <t>115561; 153842</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>98416; 135595</t>
+          <t>102561; 137620</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>126062; 153461</t>
+          <t>124397; 152945</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>124864; 159185</t>
+          <t>126034; 160684</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>140685; 180881</t>
+          <t>140721; 178181</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>136450; 171656</t>
+          <t>135201; 171006</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>136770; 179457</t>
+          <t>137974; 180210</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>100758; 138327</t>
+          <t>98412; 138833</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>129525; 172787</t>
+          <t>128765; 171394</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>131952; 173874</t>
+          <t>132473; 173491</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>223003; 466391</t>
+          <t>221618; 473614</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>235162; 286948</t>
+          <t>238379; 286456</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>282660; 340724</t>
+          <t>277713; 342180</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>281633; 335158</t>
+          <t>282486; 335719</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>390341; 687938</t>
+          <t>392210; 671417</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>152205; 183480</t>
+          <t>151617; 183320</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>173712; 217007</t>
+          <t>174044; 214432</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>191741; 234629</t>
+          <t>190924; 234361</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>181637; 219300</t>
+          <t>183041; 219081</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>111655; 152775</t>
+          <t>109259; 150352</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>133716; 176716</t>
+          <t>132230; 177480</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>153433; 202259</t>
+          <t>156100; 203457</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>159526; 193453</t>
+          <t>159640; 192255</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>268204; 327409</t>
+          <t>267877; 324842</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>319144; 382257</t>
+          <t>319686; 378899</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>361415; 426153</t>
+          <t>361080; 426342</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>354963; 401141</t>
+          <t>354763; 402129</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>704703; 777999</t>
+          <t>706023; 776905</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>822352; 917084</t>
+          <t>827419; 915256</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>858465; 945068</t>
+          <t>857980; 945922</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>757945; 846187</t>
+          <t>757511; 850378</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>535011; 619576</t>
+          <t>538793; 620420</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>699546; 792414</t>
+          <t>705813; 795939</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>695881; 792794</t>
+          <t>693930; 788550</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>801281; 1350692</t>
+          <t>803430; 1297233</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1262052; 1379693</t>
+          <t>1264825; 1381379</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1556186; 1691213</t>
+          <t>1555651; 1682935</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1583199; 1710332</t>
+          <t>1575264; 1701824</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1612998; 2158940</t>
+          <t>1614534; 2133061</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P62-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>39,23; 58,19</t>
+          <t>39,09; 57,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,97; 54,53</t>
+          <t>37,78; 53,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,96; 45,78</t>
+          <t>29,41; 45,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,26; 28,48</t>
+          <t>15,52; 29,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,41; 31,58</t>
+          <t>18,06; 31,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,55; 44,57</t>
+          <t>29,93; 45,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,67; 37,42</t>
+          <t>22,75; 37,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,78; 26,97</t>
+          <t>15,16; 23,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,21; 41,12</t>
+          <t>29,18; 40,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,33; 46,47</t>
+          <t>35,68; 46,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,12; 38,78</t>
+          <t>28,47; 39,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,95; 25,95</t>
+          <t>16,66; 24,5</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,53%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,41; 61,85</t>
+          <t>48,05; 61,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,66; 46,08</t>
+          <t>34,59; 46,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,86; 51,17</t>
+          <t>39,99; 50,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41,84; 58,69</t>
+          <t>45,27; 60,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,41; 26,18</t>
+          <t>17,77; 26,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,93; 27,79</t>
+          <t>18,59; 27,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,38; 27,16</t>
+          <t>18,64; 26,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,66; 40,5</t>
+          <t>30,67; 39,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,58; 38,24</t>
+          <t>30,45; 38,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,26; 34,98</t>
+          <t>27,39; 34,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,25; 36,33</t>
+          <t>29,46; 36,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,8; 46,78</t>
+          <t>38,57; 46,68</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,32%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44,06; 61,04</t>
+          <t>44,17; 61,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,48; 53,08</t>
+          <t>38,32; 54,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,85; 55,34</t>
+          <t>41,34; 55,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47,42; 62,73</t>
+          <t>46,26; 61,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,61; 33,52</t>
+          <t>22,25; 33,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,87; 35,47</t>
+          <t>24,12; 35,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,52; 39,03</t>
+          <t>26,4; 39,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,81; 42,22</t>
+          <t>32,19; 42,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32,12; 41,9</t>
+          <t>32,76; 42,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31,74; 40,92</t>
+          <t>31,9; 41,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,77; 44,28</t>
+          <t>35,1; 44,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40,32; 49,0</t>
+          <t>40,16; 48,52</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,73; 60,06</t>
+          <t>43,71; 60,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,66; 51,66</t>
+          <t>37,96; 51,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,98; 44,06</t>
+          <t>32,37; 44,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43,99; 64,6</t>
+          <t>45,39; 65,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,06; 33,33</t>
+          <t>22,46; 33,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,96; 41,92</t>
+          <t>31,05; 42,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,22; 33,32</t>
+          <t>22,49; 33,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,5; 42,69</t>
+          <t>31,2; 41,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,71; 41,71</t>
+          <t>32,14; 41,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,08; 44,92</t>
+          <t>35,97; 44,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,36; 36,07</t>
+          <t>28,27; 36,26</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,34; 49,42</t>
+          <t>38,97; 48,67</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>43,56%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,07; 62,63</t>
+          <t>42,08; 63,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,51; 48,61</t>
+          <t>30,4; 47,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42,91; 60,13</t>
+          <t>42,25; 59,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38,16; 60,39</t>
+          <t>37,49; 58,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,12; 29,12</t>
+          <t>16,09; 29,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,13; 36,84</t>
+          <t>22,0; 36,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,15; 42,78</t>
+          <t>27,9; 43,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>35,37; 48,12</t>
+          <t>34,46; 47,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,3; 39,16</t>
+          <t>27,18; 39,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,05; 39,29</t>
+          <t>27,51; 38,74</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,1; 47,77</t>
+          <t>36,75; 48,19</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,22; 49,94</t>
+          <t>37,72; 48,68</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>46,47; 64,83</t>
+          <t>46,87; 65,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39,96; 55,75</t>
+          <t>39,59; 55,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39,73; 55,48</t>
+          <t>39,47; 55,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51,0; 67,69</t>
+          <t>49,96; 65,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,78; 31,66</t>
+          <t>18,51; 31,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,55; 33,57</t>
+          <t>21,67; 33,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,33; 30,02</t>
+          <t>17,18; 30,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,46; 40,02</t>
+          <t>30,07; 40,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29,83; 40,89</t>
+          <t>30,59; 41,37</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,46; 40,55</t>
+          <t>30,71; 40,26</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29,43; 39,49</t>
+          <t>28,98; 39,13</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40,76; 50,11</t>
+          <t>40,71; 50,06</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>49,54%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>45,29; 57,74</t>
+          <t>45,69; 57,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36,82; 46,62</t>
+          <t>36,32; 47,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46,11; 58,32</t>
+          <t>46,42; 58,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47,78; 62,4</t>
+          <t>50,48; 64,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,55; 30,41</t>
+          <t>22,22; 30,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,41; 33,82</t>
+          <t>25,81; 33,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,37; 43,7</t>
+          <t>33,84; 43,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>41,25; 88,16</t>
+          <t>38,19; 47,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>32,44; 38,98</t>
+          <t>32,35; 39,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31,24; 38,49</t>
+          <t>31,78; 38,51</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40,93; 48,64</t>
+          <t>40,48; 48,06</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,48; 81,28</t>
+          <t>45,88; 53,84</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>49,76%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>55,5; 67,11</t>
+          <t>55,61; 67,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>42,37; 52,21</t>
+          <t>41,85; 52,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42,91; 52,67</t>
+          <t>43,53; 53,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61,5; 73,61</t>
+          <t>59,19; 71,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,12; 27,69</t>
+          <t>19,81; 27,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,6; 31,68</t>
+          <t>23,78; 31,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,4; 35,71</t>
+          <t>27,41; 35,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>36,15; 43,54</t>
+          <t>35,46; 43,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32,82; 39,8</t>
+          <t>32,98; 39,58</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32,92; 39,02</t>
+          <t>32,56; 39,27</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35,58; 42,02</t>
+          <t>35,29; 42,11</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>47,99; 54,4</t>
+          <t>46,25; 52,89</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>44,51%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>51,94; 57,15</t>
+          <t>51,86; 57,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41,76; 46,19</t>
+          <t>41,74; 46,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44,08; 48,6</t>
+          <t>43,94; 48,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51,16; 57,44</t>
+          <t>52,16; 57,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22,96; 26,44</t>
+          <t>22,86; 26,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,43; 30,93</t>
+          <t>27,22; 30,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,23; 32,08</t>
+          <t>28,2; 32,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>36,89; 59,56</t>
+          <t>35,12; 38,54</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>34,13; 37,28</t>
+          <t>34,19; 37,31</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34,15; 36,95</t>
+          <t>34,19; 37,12</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35,76; 38,64</t>
+          <t>35,92; 38,72</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>44,13; 58,3</t>
+          <t>42,86; 46,05</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>25310</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31304</t>
+          <t>31851</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55549</t>
+          <t>57162</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>42220; 62620</t>
+          <t>42067; 61762</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63394; 91038</t>
+          <t>63074; 89082</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46985; 71789</t>
+          <t>46116; 71470</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16523; 33008</t>
+          <t>17903; 34078</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25914; 47001</t>
+          <t>26883; 47617</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55571; 83801</t>
+          <t>56270; 84766</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43355; 68542</t>
+          <t>41668; 68273</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24379; 39191</t>
+          <t>24755; 39180</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74908; 105458</t>
+          <t>74845; 104483</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>125406; 164959</t>
+          <t>126659; 165298</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>95594; 131838</t>
+          <t>96791; 133506</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44275; 67792</t>
+          <t>46421; 68267</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>134827</t>
+          <t>143060</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>122029</t>
+          <t>126989</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>256856</t>
+          <t>270049</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>107765; 137682</t>
+          <t>106948; 136645</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>114128; 151731</t>
+          <t>113881; 152255</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>130532; 167579</t>
+          <t>130950; 166142</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>112546; 157882</t>
+          <t>122858; 162994</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64308; 96703</t>
+          <t>65611; 96430</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74503; 109368</t>
+          <t>73174; 108717</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75009; 110850</t>
+          <t>76066; 110020</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>107931; 138054</t>
+          <t>111483; 143245</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>180999; 226374</t>
+          <t>180213; 228739</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>197035; 252860</t>
+          <t>197966; 250721</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>215154; 267229</t>
+          <t>216727; 269224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>230554; 285318</t>
+          <t>244893; 296355</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91782</t>
+          <t>90091</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83726</t>
+          <t>86104</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>175507</t>
+          <t>176195</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>63072; 87370</t>
+          <t>63230; 87681</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>69223; 95496</t>
+          <t>68944; 97967</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75979; 102930</t>
+          <t>76878; 103262</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78898; 104381</t>
+          <t>76546; 102112</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>54449; 80725</t>
+          <t>53593; 81495</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61260; 91024</t>
+          <t>61893; 92255</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65184; 95907</t>
+          <t>64890; 96517</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>72240; 95867</t>
+          <t>74730; 97670</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>123323; 160881</t>
+          <t>125779; 162214</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>138540; 178628</t>
+          <t>139234; 181011</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>150096; 191174</t>
+          <t>151557; 192419</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>158649; 192816</t>
+          <t>159661; 192910</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>79018</t>
+          <t>88914</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>80696</t>
+          <t>86066</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>159713</t>
+          <t>174980</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58656; 80572</t>
+          <t>58637; 81127</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88304; 117997</t>
+          <t>86699; 118313</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80586; 111037</t>
+          <t>81562; 111843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>63227; 92849</t>
+          <t>71949; 103269</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>51929; 78451</t>
+          <t>52855; 78785</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>86887; 117632</t>
+          <t>87125; 118367</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66508; 99751</t>
+          <t>67312; 100926</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69887; 91791</t>
+          <t>74545; 98650</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>117182; 154133</t>
+          <t>118763; 153127</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>183638; 228671</t>
+          <t>183108; 226415</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>156338; 198842</t>
+          <t>155865; 199889</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>141114; 177293</t>
+          <t>154858; 193399</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31396</t>
+          <t>33457</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>41657</t>
+          <t>43271</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73053</t>
+          <t>76728</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36466; 54297</t>
+          <t>36480; 54742</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>39438; 62835</t>
+          <t>39289; 61571</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55907; 78343</t>
+          <t>55043; 77500</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24613; 38953</t>
+          <t>26061; 40686</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25349; 45790</t>
+          <t>25308; 45856</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36051; 60004</t>
+          <t>35840; 59731</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44032; 69375</t>
+          <t>45238; 70310</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>35523; 48320</t>
+          <t>36738; 50698</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>66605; 95535</t>
+          <t>66312; 96086</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>81943; 114793</t>
+          <t>80373; 113170</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>108499; 139706</t>
+          <t>107469; 140947</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>63036; 82364</t>
+          <t>66442; 85732</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>79936</t>
+          <t>79086</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>59936</t>
+          <t>61298</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>139872</t>
+          <t>140384</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>52853; 73735</t>
+          <t>53303; 74468</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>61807; 86235</t>
+          <t>61233; 86346</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61823; 86332</t>
+          <t>61424; 86221</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>68637; 91088</t>
+          <t>67254; 88748</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>36685; 61833</t>
+          <t>36149; 61270</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48436; 75438</t>
+          <t>48707; 75193</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33428; 57900</t>
+          <t>33139; 58405</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>50277; 68298</t>
+          <t>53035; 71369</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>92191; 126388</t>
+          <t>94542; 127872</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>115561; 153842</t>
+          <t>116504; 152762</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>102561; 137620</t>
+          <t>100981; 136361</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>124397; 152945</t>
+          <t>126604; 155696</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>158673</t>
+          <t>190427</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>347820</t>
+          <t>173594</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>506493</t>
+          <t>364021</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>126034; 160684</t>
+          <t>127132; 160828</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>140721; 178181</t>
+          <t>138815; 179775</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>135201; 171006</t>
+          <t>136107; 172166</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>137974; 180210</t>
+          <t>167054; 212568</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>98412; 138833</t>
+          <t>101473; 137912</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>128765; 171394</t>
+          <t>130813; 171440</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>132473; 173491</t>
+          <t>134364; 174592</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>221618; 473614</t>
+          <t>154222; 192750</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>238379; 286456</t>
+          <t>237742; 288591</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>277713; 342180</t>
+          <t>282569; 342332</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>282486; 335719</t>
+          <t>279432; 331721</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>392210; 671417</t>
+          <t>337112; 395582</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>201594</t>
+          <t>224104</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>175796</t>
+          <t>201590</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>377390</t>
+          <t>425695</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>151617; 183320</t>
+          <t>151904; 184024</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>174044; 214432</t>
+          <t>171910; 215360</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>190924; 234361</t>
+          <t>193708; 236140</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>183041; 219081</t>
+          <t>201291; 243321</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>109259; 150352</t>
+          <t>107564; 148470</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>132230; 177480</t>
+          <t>133212; 177789</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>156100; 203457</t>
+          <t>156149; 201957</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>159640; 192255</t>
+          <t>182729; 222877</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>267877; 324842</t>
+          <t>269154; 323065</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>319686; 378899</t>
+          <t>316112; 381297</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>361080; 426342</t>
+          <t>358079; 427288</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>354763; 402129</t>
+          <t>395686; 452500</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>801470</t>
+          <t>874450</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>942962</t>
+          <t>810764</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1744432</t>
+          <t>1685213</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>706023; 776905</t>
+          <t>704978; 776480</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>827419; 915256</t>
+          <t>827071; 916749</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>857980; 945922</t>
+          <t>855290; 942040</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>757511; 850378</t>
+          <t>827195; 916420</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>538793; 620420</t>
+          <t>536304; 621544</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>705813; 795939</t>
+          <t>700539; 796120</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>693930; 788550</t>
+          <t>693138; 788114</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>803430; 1297233</t>
+          <t>772622; 847928</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1264825; 1381379</t>
+          <t>1267016; 1382544</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1555651; 1682935</t>
+          <t>1557149; 1690707</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1575264; 1701824</t>
+          <t>1582330; 1705488</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1614534; 2133061</t>
+          <t>1622520; 1743348</t>
         </is>
       </c>
     </row>
